--- a/reports/二级子公司D_利润表_2026-07.xlsx
+++ b/reports/二级子公司D_利润表_2026-07.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>95287490</v>
+        <v>97453867</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>93162381</v>
+        <v>93250770</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>580077930</v>
+        <v>580655000</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>321314</v>
+        <v>321984</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2000370</v>
+        <v>2000930</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>276312</v>
+        <v>276642</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1715036</v>
+        <v>1714853</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>232084</v>
+        <v>231114</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1430593</v>
+        <v>1428958</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>207650</v>
+        <v>208461</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1286787</v>
+        <v>1286091</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>114677</v>
+        <v>115987</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>714321</v>
+        <v>714568</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>92471</v>
+        <v>92842</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>571941</v>
+        <v>571749</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>94042982</v>
+        <v>96206837</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>91917873</v>
+        <v>92003740</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>5170463</v>
+        <v>5200909</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>32150027</v>
+        <v>32178694</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>405813</v>
+        <v>403505</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2503222</v>
+        <v>2503024</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>693743</v>
+        <v>690067</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>4290390</v>
+        <v>4290954</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>82573100</v>
+        <v>82653575</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>514332905</v>
+        <v>514878154</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1383876</v>
+        <v>1376175</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>8576787</v>
+        <v>8580090</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>464190</v>
+        <v>458741</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2861272</v>
+        <v>2859493</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2303321</v>
+        <v>2296163</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>14294806</v>
+        <v>14294602</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>573688</v>
+        <v>575140</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3571743</v>
+        <v>3573013</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2083735</v>
+        <v>2075515</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>12871045</v>
+        <v>12861237</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>41374</v>
+        <v>41284</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>288565</v>
+        <v>288313</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1251079</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>7716629</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>835219</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5145000</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>62520913</v>
+        <v>67568295</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>56080902</v>
+        <v>56622426</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>55041229</v>
+        <v>55582580</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>342874885</v>
+        <v>343193147</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1039673</v>
+        <v>1039846</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>6433866</v>
+        <v>6435847</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2074472</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>12872774</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>662274</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4119296</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>413190</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2574351</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>495395</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3088762</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>371612</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2316129</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>248038</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1543776</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>207113</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1286258</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>986443</v>
+        <v>980435</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>6080177</v>
+        <v>6073294</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>749034</v>
+        <v>751597</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>4646147</v>
+        <v>4644103</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>573548</v>
+        <v>579340</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>3571673</v>
+        <v>3572552</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4396695</v>
+        <v>4408612</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>27170430</v>
+        <v>27154713</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>155217</v>
+        <v>174073</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1082141</v>
+        <v>1072087</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>328108</v>
+        <v>331315</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2306455</v>
+        <v>2306831</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>369643</v>
+        <v>331315</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2594340</v>
+        <v>2306831</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>41430</v>
+        <v>41250</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>288541</v>
+        <v>288441</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>166643</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1168335</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>362081</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2252726</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>110657</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>778967</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>82931</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>584196</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>138263</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>973562</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>516863</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3216121</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>73992</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>519080</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>55632</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>389256</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>92946</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>648692</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>65190</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>454062</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>46618</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>324336</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>37300</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>259489</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27950</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>194642</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>31522069</v>
+        <v>29869635</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>36168984</v>
+        <v>33325051</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>207310</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1287289</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>46171</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>324566</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>72483</v>
+        <v>71711</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>504924</v>
+        <v>504885</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>31449586</v>
+        <v>30005234</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2559711</v>
+        <v>2560734</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>18014768</v>
+        <v>18028618</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>28889875</v>
+        <v>27444500</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>28889875</v>
+        <v>27444500</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>28889875</v>
+        <v>27444500</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>28889875</v>
+        <v>27444500</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>28889875</v>
+        <v>27444500</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
